--- a/artfynd/A 26070-2026 artfynd.xlsx
+++ b/artfynd/A 26070-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1809,6 +1809,347 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135213431</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91995</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lötberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>557867</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6420420</v>
+      </c>
+      <c r="S13" t="n">
+        <v>9</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hycklinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135211354</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lötberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>557751</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6420388</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hycklinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135212138</v>
+      </c>
+      <c r="B15" t="n">
+        <v>43314</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>201146</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Silverblåvinge</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Polyommatus amandus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lötberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>557725</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6420500</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hycklinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26070-2026 artfynd.xlsx
+++ b/artfynd/A 26070-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1087,54 +1087,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134940466</v>
+        <v>135227386</v>
       </c>
       <c r="B6" t="n">
-        <v>99195</v>
+        <v>57153</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lötberget, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557596</v>
+        <v>557692</v>
       </c>
       <c r="R6" t="n">
-        <v>6420387</v>
+        <v>6420279</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,12 +1152,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1186,64 +1177,59 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134941665</v>
+        <v>135233378</v>
       </c>
       <c r="B7" t="n">
-        <v>99195</v>
+        <v>58136</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lötberget, Ög</t>
+          <t>Åkersholm, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557617</v>
+        <v>557634</v>
       </c>
       <c r="R7" t="n">
-        <v>6420381</v>
+        <v>6420356</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1267,12 +1253,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,14 +1278,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134941856</v>
+        <v>134940466</v>
       </c>
       <c r="B8" t="n">
         <v>99195</v>
@@ -1329,7 +1315,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1343,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557616</v>
+        <v>557596</v>
       </c>
       <c r="R8" t="n">
-        <v>6420361</v>
+        <v>6420387</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,7 +1391,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134942017</v>
+        <v>134941665</v>
       </c>
       <c r="B9" t="n">
         <v>99195</v>
@@ -1435,7 +1421,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1449,10 +1435,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557649</v>
+        <v>557617</v>
       </c>
       <c r="R9" t="n">
-        <v>6420350</v>
+        <v>6420381</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,7 +1497,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134943388</v>
+        <v>134941856</v>
       </c>
       <c r="B10" t="n">
         <v>99195</v>
@@ -1541,7 +1527,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1555,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557692</v>
+        <v>557616</v>
       </c>
       <c r="R10" t="n">
-        <v>6420279</v>
+        <v>6420361</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,45 +1603,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134942868</v>
+        <v>134942017</v>
       </c>
       <c r="B11" t="n">
-        <v>106324</v>
+        <v>99195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lötberget, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557675</v>
+        <v>557649</v>
       </c>
       <c r="R11" t="n">
-        <v>6420324</v>
+        <v>6420350</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,45 +1709,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134943864</v>
+        <v>134943388</v>
       </c>
       <c r="B12" t="n">
-        <v>97435</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lötberget, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557804</v>
+        <v>557692</v>
       </c>
       <c r="R12" t="n">
-        <v>6420302</v>
+        <v>6420279</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,51 +1815,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135213431</v>
+        <v>134942868</v>
       </c>
       <c r="B13" t="n">
-        <v>91995</v>
+        <v>106324</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lötberget, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557867</v>
+        <v>557675</v>
       </c>
       <c r="R13" t="n">
-        <v>6420420</v>
+        <v>6420324</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1879,22 +1880,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>18:11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>18:11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,68 +1900,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emma Nordenberg, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135211354</v>
+        <v>134943864</v>
       </c>
       <c r="B14" t="n">
-        <v>58131</v>
+        <v>97435</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103023</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lötberget, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557751</v>
+        <v>557804</v>
       </c>
       <c r="R14" t="n">
-        <v>6420388</v>
+        <v>6420302</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1994,22 +1977,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:55</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:55</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2024,69 +1997,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emma Nordenberg, Hugo Axelsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135212138</v>
+        <v>135229545</v>
       </c>
       <c r="B15" t="n">
-        <v>43314</v>
+        <v>97435</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>201146</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Polyommatus amandus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schneider, 1792)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lötberget, Ög</t>
+          <t>Åkersholm, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557725</v>
+        <v>557935</v>
       </c>
       <c r="R15" t="n">
-        <v>6420500</v>
+        <v>6420383</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2110,22 +2074,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>17:25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>17:25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2140,15 +2094,647 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135229026</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92188</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3008</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Timmerticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Amyloporia sinuosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Åkersholm, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>558009</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6420404</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hycklinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135213431</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91995</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lötberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>557867</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6420420</v>
+      </c>
+      <c r="S17" t="n">
+        <v>9</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hycklinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Anna Grimlycke</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Anna Grimlycke</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135229087</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91995</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Åkersholm, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>557999</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6420420</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hycklinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135229374</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91995</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Åkersholm, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>557935</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6420383</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hycklinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135211354</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lötberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>557751</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6420388</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hycklinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135212138</v>
+      </c>
+      <c r="B21" t="n">
+        <v>43314</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>201146</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Silverblåvinge</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Polyommatus amandus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lötberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>557725</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6420500</v>
+      </c>
+      <c r="S21" t="n">
+        <v>6</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hycklinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26070-2026 artfynd.xlsx
+++ b/artfynd/A 26070-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134942095</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134941912</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134942003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134943354</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135227386</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135233378</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1388,6 +1423,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134940466</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1494,6 +1534,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134941665</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1600,6 +1645,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134941856</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1706,6 +1756,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134942017</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1812,6 +1867,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134943388</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1909,6 +1969,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134942868</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2006,6 +2071,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134943864</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2103,6 +2173,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229545</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2200,6 +2275,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229026</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2310,6 +2390,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135213431</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2407,6 +2492,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229087</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2504,6 +2594,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229374</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2619,6 +2714,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135211354</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2735,8 +2835,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135212138</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 26070-2026 artfynd.xlsx
+++ b/artfynd/A 26070-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134942095</v>
       </c>
       <c r="B2" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>134941912</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>134942003</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>134943354</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>135227386</v>
       </c>
       <c r="B6" t="n">
-        <v>57153</v>
+        <v>57158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>135233378</v>
       </c>
       <c r="B7" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>134940466</v>
       </c>
       <c r="B8" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>134941665</v>
       </c>
       <c r="B9" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>134941856</v>
       </c>
       <c r="B10" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>134942017</v>
       </c>
       <c r="B11" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>134943388</v>
       </c>
       <c r="B12" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>134942868</v>
       </c>
       <c r="B13" t="n">
-        <v>106324</v>
+        <v>106379</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>134943864</v>
       </c>
       <c r="B14" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>135229545</v>
       </c>
       <c r="B15" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>135229026</v>
       </c>
       <c r="B16" t="n">
-        <v>92188</v>
+        <v>92230</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>135213431</v>
       </c>
       <c r="B17" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>135229087</v>
       </c>
       <c r="B18" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>135229374</v>
       </c>
       <c r="B19" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>135211354</v>
       </c>
       <c r="B20" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>135212138</v>
       </c>
       <c r="B21" t="n">
-        <v>43314</v>
+        <v>43319</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 26070-2026 artfynd.xlsx
+++ b/artfynd/A 26070-2026 artfynd.xlsx
@@ -2082,7 +2082,7 @@
         <v>135229545</v>
       </c>
       <c r="B15" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>135229026</v>
       </c>
       <c r="B16" t="n">
-        <v>92230</v>
+        <v>92257</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>135213431</v>
       </c>
       <c r="B17" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>135229087</v>
       </c>
       <c r="B18" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>135229374</v>
       </c>
       <c r="B19" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 26070-2026 artfynd.xlsx
+++ b/artfynd/A 26070-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1112,54 +1112,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134940466</v>
+        <v>135227386</v>
       </c>
       <c r="B6" t="n">
-        <v>99242</v>
+        <v>57158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lötberget, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557596</v>
+        <v>557692</v>
       </c>
       <c r="R6" t="n">
-        <v>6420387</v>
+        <v>6420279</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,12 +1177,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,69 +1202,64 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134940466</t>
+          <t>https://artportalen.se/Sighting/135227386</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134941665</v>
+        <v>135233378</v>
       </c>
       <c r="B7" t="n">
-        <v>99242</v>
+        <v>58141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lötberget, Ög</t>
+          <t>Åkersholm, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557617</v>
+        <v>557634</v>
       </c>
       <c r="R7" t="n">
-        <v>6420381</v>
+        <v>6420356</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,12 +1283,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,19 +1308,19 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Hugo Axelsson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134941665</t>
+          <t>https://artportalen.se/Sighting/135233378</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134941856</v>
+        <v>134940466</v>
       </c>
       <c r="B8" t="n">
         <v>99242</v>
@@ -1364,7 +1350,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1378,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557616</v>
+        <v>557596</v>
       </c>
       <c r="R8" t="n">
-        <v>6420361</v>
+        <v>6420387</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,13 +1425,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134941856</t>
+          <t>https://artportalen.se/Sighting/134940466</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134942017</v>
+        <v>134941665</v>
       </c>
       <c r="B9" t="n">
         <v>99242</v>
@@ -1475,7 +1461,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1489,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557649</v>
+        <v>557617</v>
       </c>
       <c r="R9" t="n">
-        <v>6420350</v>
+        <v>6420381</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,13 +1536,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134942017</t>
+          <t>https://artportalen.se/Sighting/134941665</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134943388</v>
+        <v>134941856</v>
       </c>
       <c r="B10" t="n">
         <v>99242</v>
@@ -1586,7 +1572,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1600,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557692</v>
+        <v>557616</v>
       </c>
       <c r="R10" t="n">
-        <v>6420279</v>
+        <v>6420361</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,51 +1647,60 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134943388</t>
+          <t>https://artportalen.se/Sighting/134941856</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134942868</v>
+        <v>134942017</v>
       </c>
       <c r="B11" t="n">
-        <v>106379</v>
+        <v>99242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lötberget, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557675</v>
+        <v>557649</v>
       </c>
       <c r="R11" t="n">
-        <v>6420324</v>
+        <v>6420350</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,51 +1758,60 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134942868</t>
+          <t>https://artportalen.se/Sighting/134942017</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134943864</v>
+        <v>134943388</v>
       </c>
       <c r="B12" t="n">
-        <v>97479</v>
+        <v>99242</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lötberget, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557804</v>
+        <v>557692</v>
       </c>
       <c r="R12" t="n">
-        <v>6420302</v>
+        <v>6420279</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1869,975 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/134943388</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134942868</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106379</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lötberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>557675</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6420324</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hycklinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Hugo Axelsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134942868</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134943864</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97479</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>53</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lötberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>557804</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6420302</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hycklinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Hugo Axelsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134943864</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135229545</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97511</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>53</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Åkersholm, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>557935</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6420383</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hycklinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229545</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135229026</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92262</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3008</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Timmerticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Amyloporia sinuosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Åkersholm, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>558009</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6420404</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hycklinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135213431</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92069</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lötberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>557867</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6420420</v>
+      </c>
+      <c r="S17" t="n">
+        <v>9</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hycklinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135213431</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135229087</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92069</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Åkersholm, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>557999</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6420420</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hycklinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229087</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135229374</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92069</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Åkersholm, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>557935</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6420383</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hycklinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135229374</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135211354</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lötberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>557751</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6420388</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hycklinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135211354</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135212138</v>
+      </c>
+      <c r="B21" t="n">
+        <v>43319</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>201146</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Silverblåvinge</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Polyommatus amandus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lötberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>557725</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6420500</v>
+      </c>
+      <c r="S21" t="n">
+        <v>6</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hycklinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anna Grimlycke</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135212138</t>
         </is>
       </c>
     </row>
@@ -1882,6 +2854,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26070-2026 artfynd.xlsx
+++ b/artfynd/A 26070-2026 artfynd.xlsx
@@ -2082,7 +2082,7 @@
         <v>135229545</v>
       </c>
       <c r="B15" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>135229026</v>
       </c>
       <c r="B16" t="n">
-        <v>92262</v>
+        <v>92264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>135213431</v>
       </c>
       <c r="B17" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>135229087</v>
       </c>
       <c r="B18" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>135229374</v>
       </c>
       <c r="B19" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
